--- a/crm/backend/src/assets/po_template.xlsx
+++ b/crm/backend/src/assets/po_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kvb-crm\backend\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69FA8682-5E82-4FDC-9167-753F6D83E80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402D7EAE-A99A-41DC-8C63-B8EE147E09DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase Order Template" sheetId="1" r:id="rId1"/>
@@ -261,7 +261,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,12 +286,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -518,6 +512,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -543,60 +562,35 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="15" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1061,30 +1055,30 @@
   </cols>
   <sheetData>
     <row r="4" spans="9:14" ht="75" customHeight="1">
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="26"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="9:14" ht="18" customHeight="1">
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
     </row>
     <row r="6" spans="9:14" ht="18" customHeight="1">
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="J6" s="31" t="s">
+      <c r="J6" s="30" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="32" t="s">
@@ -1097,104 +1091,104 @@
       <c r="N6" s="33"/>
     </row>
     <row r="7" spans="9:14" ht="18" customHeight="1">
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28" t="s">
+      <c r="J7" s="17"/>
+      <c r="K7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
     </row>
     <row r="8" spans="9:14" ht="18" customHeight="1">
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="21" t="s">
+      <c r="J8" s="34"/>
+      <c r="K8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
     </row>
     <row r="9" spans="9:14" ht="18" customHeight="1">
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="21" t="s">
+      <c r="J9" s="34"/>
+      <c r="K9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="23"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="9:14" ht="18" customHeight="1">
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29" t="s">
+      <c r="J10" s="34"/>
+      <c r="K10" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
     </row>
     <row r="11" spans="9:14" ht="18" customHeight="1">
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29" t="s">
+      <c r="J11" s="34"/>
+      <c r="K11" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
     </row>
     <row r="12" spans="9:14" ht="18" customHeight="1">
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="29"/>
-      <c r="K12" s="21" t="s">
+      <c r="J12" s="34"/>
+      <c r="K12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
     </row>
     <row r="13" spans="9:14" ht="18" customHeight="1">
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22" t="s">
+      <c r="J13" s="20"/>
+      <c r="K13" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22" t="s">
+      <c r="L13" s="20"/>
+      <c r="M13" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="22"/>
+      <c r="N13" s="20"/>
     </row>
     <row r="14" spans="9:14" ht="18" customHeight="1">
       <c r="I14" s="4"/>
       <c r="J14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="K14" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="35"/>
-      <c r="M14" s="36">
+      <c r="L14" s="36"/>
+      <c r="M14" s="37">
         <v>46131</v>
       </c>
-      <c r="N14" s="37"/>
+      <c r="N14" s="38"/>
     </row>
     <row r="15" spans="9:14" ht="18" customHeight="1">
       <c r="I15" s="4" t="s">
@@ -1404,12 +1398,12 @@
       </c>
     </row>
     <row r="32" spans="9:17" ht="18" customHeight="1">
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
       <c r="M32" s="5" t="s">
         <v>17</v>
       </c>
@@ -1419,32 +1413,32 @@
       </c>
     </row>
     <row r="33" spans="9:14" ht="18" customHeight="1">
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="38" t="s">
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="12" t="s">
         <v>32</v>
       </c>
       <c r="N33" s="39"/>
     </row>
     <row r="34" spans="9:14" ht="18" customHeight="1">
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="38" t="s">
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="12" t="s">
         <v>33</v>
       </c>
       <c r="N34" s="40"/>
     </row>
     <row r="35" spans="9:14" ht="18" customHeight="1">
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
       <c r="M35" s="5" t="s">
         <v>19</v>
       </c>
@@ -1454,35 +1448,29 @@
       </c>
     </row>
     <row r="36" spans="9:14" ht="18" customHeight="1">
-      <c r="I36" s="14"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="16"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="25"/>
     </row>
     <row r="37" spans="9:14" ht="18" customHeight="1">
-      <c r="I37" s="17"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="19"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:N37"/>
+    <mergeCell ref="I33:L34"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="I12:J12"/>
@@ -1490,12 +1478,18 @@
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="M13:N13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:N37"/>
-    <mergeCell ref="I33:L34"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:N7"/>
   </mergeCells>
   <conditionalFormatting sqref="I7">
     <cfRule type="colorScale" priority="3">
